--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2021_magallanes.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2021_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:43</t>
+    <t xml:space="preserve">2026-10-05 21:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2095,7 +2095,7 @@
         <v>12</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="93">
@@ -3081,7 +3081,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="151">
